--- a/dialect_frontend/frontend/dialect/sinmin/syllable.xlsx
+++ b/dialect_frontend/frontend/dialect/sinmin/syllable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7052" uniqueCount="3741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7168" uniqueCount="3797">
   <si>
     <t>pinyin</t>
   </si>
@@ -37,7 +37,7 @@
     <t>t</t>
   </si>
   <si>
-    <t>ʊ⁵⁴,ŋ</t>
+    <t>ˈʊ⁵⁴,ŋ</t>
   </si>
   <si>
     <t>dung5</t>
@@ -46,7 +46,7 @@
     <t>tʊŋ⁵¹</t>
   </si>
   <si>
-    <t>ʊ⁵¹,ŋ</t>
+    <t>ˈʊ⁵¹,ŋ</t>
   </si>
   <si>
     <t>tung2</t>
@@ -58,7 +58,7 @@
     <t>tʰ</t>
   </si>
   <si>
-    <t>ʊ²⁴,ŋ</t>
+    <t>ˈʊ²⁴,ŋ</t>
   </si>
   <si>
     <t>tung5</t>
@@ -73,7 +73,7 @@
     <t>tʰɛn²⁴</t>
   </si>
   <si>
-    <t>ɛ²⁴,n</t>
+    <t>ˈɛ²⁴,n</t>
   </si>
   <si>
     <t>zung5</t>
@@ -112,7 +112,7 @@
     <t>t͜sʊŋ³¹</t>
   </si>
   <si>
-    <t>ʊ³¹,ŋ</t>
+    <t>ˈʊ³¹,ŋ</t>
   </si>
   <si>
     <t>sung1</t>
@@ -157,7 +157,7 @@
     <t>t͜sʰim⁵⁴</t>
   </si>
   <si>
-    <t>i⁵⁴,m</t>
+    <t>ˈi⁵⁴,m</t>
   </si>
   <si>
     <t>shung1</t>
@@ -223,7 +223,7 @@
     <t>fam⁵¹</t>
   </si>
   <si>
-    <t>a⁵¹,m</t>
+    <t>ˈa⁵¹,m</t>
   </si>
   <si>
     <t>fung1</t>
@@ -253,7 +253,7 @@
     <t>kɔŋ⁵⁴</t>
   </si>
   <si>
-    <t>ɔ⁵⁴,ŋ</t>
+    <t>ˈɔ⁵⁴,ŋ</t>
   </si>
   <si>
     <t>lung1</t>
@@ -307,7 +307,7 @@
     <t>nɔ²⁴</t>
   </si>
   <si>
-    <t>ɔ²⁴</t>
+    <t>ˈɔ²⁴</t>
   </si>
   <si>
     <t>sung5</t>
@@ -364,7 +364,7 @@
     <t>mɔŋ²⁴</t>
   </si>
   <si>
-    <t>ɔ²⁴,ŋ</t>
+    <t>ˈɔ²⁴,ŋ</t>
   </si>
   <si>
     <t>nong2</t>
@@ -400,7 +400,7 @@
     <t>kɔŋ⁵¹</t>
   </si>
   <si>
-    <t>ɔ⁵¹,ŋ</t>
+    <t>ˈɔ⁵¹,ŋ</t>
   </si>
   <si>
     <t>pong1</t>
@@ -445,7 +445,7 @@
     <t>kʰiɔŋ⁵⁴</t>
   </si>
   <si>
-    <t>i,ɔ⁵⁴,ŋ</t>
+    <t>i,ˈɔ⁵⁴,ŋ</t>
   </si>
   <si>
     <t>kong1</t>
@@ -460,7 +460,7 @@
     <t>t͜sʰiɔŋ²⁴</t>
   </si>
   <si>
-    <t>i,ɔ²⁴,ŋ</t>
+    <t>i,ˈɔ²⁴,ŋ</t>
   </si>
   <si>
     <t>cong5</t>
@@ -487,7 +487,7 @@
     <t>t͜si⁵⁴</t>
   </si>
   <si>
-    <t>i⁵⁴</t>
+    <t>ˈi⁵⁴</t>
   </si>
   <si>
     <t>zak7</t>
@@ -496,7 +496,7 @@
     <t>t͜sak³</t>
   </si>
   <si>
-    <t>a³,k</t>
+    <t>ˈa³,k</t>
   </si>
   <si>
     <t>zik7</t>
@@ -505,7 +505,7 @@
     <t>t͜sik³</t>
   </si>
   <si>
-    <t>i³,k</t>
+    <t>ˈɪ³,k</t>
   </si>
   <si>
     <t>shi5</t>
@@ -514,7 +514,7 @@
     <t>ʂi⁵¹</t>
   </si>
   <si>
-    <t>i⁵¹</t>
+    <t>ˈi⁵¹</t>
   </si>
   <si>
     <t>ni3</t>
@@ -523,7 +523,7 @@
     <t>ni³¹</t>
   </si>
   <si>
-    <t>i³¹</t>
+    <t>ˈi³¹</t>
   </si>
   <si>
     <t>ji2</t>
@@ -532,7 +532,7 @@
     <t>ji²⁴</t>
   </si>
   <si>
-    <t>i²⁴</t>
+    <t>ˈi²⁴</t>
   </si>
   <si>
     <t>sha2</t>
@@ -541,7 +541,7 @@
     <t>ʂa²⁴</t>
   </si>
   <si>
-    <t>a²⁴</t>
+    <t>ˈa²⁴</t>
   </si>
   <si>
     <t>vui5</t>
@@ -550,7 +550,7 @@
     <t>vui⁵¹</t>
   </si>
   <si>
-    <t>u,i⁵¹</t>
+    <t>u,ˈi⁵¹</t>
   </si>
   <si>
     <t>vui2</t>
@@ -559,7 +559,7 @@
     <t>vui²⁴</t>
   </si>
   <si>
-    <t>u,i²⁴</t>
+    <t>u,ˈi²⁴</t>
   </si>
   <si>
     <t>gui1</t>
@@ -568,7 +568,7 @@
     <t>kui⁵⁴</t>
   </si>
   <si>
-    <t>u,i⁵⁴</t>
+    <t>u,ˈi⁵⁴</t>
   </si>
   <si>
     <t>fui1</t>
@@ -589,7 +589,7 @@
     <t>vui³¹</t>
   </si>
   <si>
-    <t>u,i³¹</t>
+    <t>u,ˈi³¹</t>
   </si>
   <si>
     <t>vo1</t>
@@ -598,7 +598,7 @@
     <t>vɔ⁵⁴</t>
   </si>
   <si>
-    <t>ɔ⁵⁴</t>
+    <t>ˈɔ⁵⁴</t>
   </si>
   <si>
     <t>mi2</t>
@@ -613,7 +613,7 @@
     <t>tʰɔ⁵¹</t>
   </si>
   <si>
-    <t>ɔ⁵¹</t>
+    <t>ˈɔ⁵¹</t>
   </si>
   <si>
     <t>hui1</t>
@@ -646,7 +646,7 @@
     <t>t͜sʰɔi⁵⁴</t>
   </si>
   <si>
-    <t>ɔ⁵⁴,i</t>
+    <t>ˈɔ⁵⁴,i</t>
   </si>
   <si>
     <t>cui1</t>
@@ -739,7 +739,7 @@
     <t>∅ŋ̍²⁴</t>
   </si>
   <si>
-    <t>ŋ̍²⁴</t>
+    <t>ˈŋ̍²⁴</t>
   </si>
   <si>
     <t>ji3</t>
@@ -760,7 +760,7 @@
     <t>ŋai²⁴</t>
   </si>
   <si>
-    <t>a²⁴,i</t>
+    <t>ˈa²⁴,i</t>
   </si>
   <si>
     <t>njai2</t>
@@ -781,7 +781,7 @@
     <t>pʰa⁵¹</t>
   </si>
   <si>
-    <t>a⁵¹</t>
+    <t>ˈa⁵¹</t>
   </si>
   <si>
     <t>ti2</t>
@@ -808,7 +808,7 @@
     <t>∅n̩⁵⁴</t>
   </si>
   <si>
-    <t>n̩⁵⁴</t>
+    <t>ˈn̩⁵⁴</t>
   </si>
   <si>
     <t>li2</t>
@@ -835,7 +835,7 @@
     <t>t͜sʰu⁵⁴</t>
   </si>
   <si>
-    <t>u⁵⁴</t>
+    <t>ˈu⁵⁴</t>
   </si>
   <si>
     <t>cu2</t>
@@ -844,7 +844,7 @@
     <t>t͜sʰu²⁴</t>
   </si>
   <si>
-    <t>u²⁴</t>
+    <t>ˈu²⁴</t>
   </si>
   <si>
     <t>cu3</t>
@@ -853,7 +853,7 @@
     <t>t͜sʰu³¹</t>
   </si>
   <si>
-    <t>u³¹</t>
+    <t>ˈu³¹</t>
   </si>
   <si>
     <t>zi3</t>
@@ -892,7 +892,7 @@
     <t>t͜sʰai⁵⁴</t>
   </si>
   <si>
-    <t>a⁵⁴,i</t>
+    <t>ˈa⁵⁴,i</t>
   </si>
   <si>
     <t>ci1</t>
@@ -907,7 +907,7 @@
     <t>t͜sʰa⁵⁴</t>
   </si>
   <si>
-    <t>a⁵⁴</t>
+    <t>ˈa⁵⁴</t>
   </si>
   <si>
     <t>ci2</t>
@@ -958,7 +958,7 @@
     <t>jin²⁴</t>
   </si>
   <si>
-    <t>i²⁴,n</t>
+    <t>ˈi²⁴,n</t>
   </si>
   <si>
     <t>sien5</t>
@@ -967,7 +967,7 @@
     <t>siɛn⁵¹</t>
   </si>
   <si>
-    <t>i,ɛ⁵¹,n</t>
+    <t>i,ˈɛ⁵¹,n</t>
   </si>
   <si>
     <t>su1</t>
@@ -982,7 +982,7 @@
     <t>sɛi⁵⁴</t>
   </si>
   <si>
-    <t>ɛ⁵⁴,i</t>
+    <t>ˈɛ⁵⁴,i</t>
   </si>
   <si>
     <t>bi3</t>
@@ -1003,7 +1003,7 @@
     <t>nɛi²⁴</t>
   </si>
   <si>
-    <t>ɛ²⁴,i</t>
+    <t>ˈɛ²⁴,i</t>
   </si>
   <si>
     <t>ni2</t>
@@ -1030,7 +1030,7 @@
     <t>hiap⁵</t>
   </si>
   <si>
-    <t>i,a⁵,p</t>
+    <t>i,ˈa⁵,p</t>
   </si>
   <si>
     <t>kui2</t>
@@ -1051,7 +1051,7 @@
     <t>tʰap³</t>
   </si>
   <si>
-    <t>a³,p</t>
+    <t>ˈa³,p</t>
   </si>
   <si>
     <t>lui5</t>
@@ -1072,7 +1072,7 @@
     <t>mɔi²⁴</t>
   </si>
   <si>
-    <t>ɔ²⁴,i</t>
+    <t>ˈɔ²⁴,i</t>
   </si>
   <si>
     <t>tui1</t>
@@ -1111,7 +1111,7 @@
     <t>su⁵¹</t>
   </si>
   <si>
-    <t>u⁵¹</t>
+    <t>ˈu⁵¹</t>
   </si>
   <si>
     <t>mau2</t>
@@ -1120,7 +1120,7 @@
     <t>mau²⁴</t>
   </si>
   <si>
-    <t>a²⁴,u</t>
+    <t>ˈa²⁴,u</t>
   </si>
   <si>
     <t>ca2</t>
@@ -1165,7 +1165,7 @@
     <t>t͜sai³¹</t>
   </si>
   <si>
-    <t>a³¹,i</t>
+    <t>ˈa³¹,i</t>
   </si>
   <si>
     <t>zu3</t>
@@ -1240,7 +1240,7 @@
     <t>nɛn⁵¹</t>
   </si>
   <si>
-    <t>ɛ⁵¹,n</t>
+    <t>ˈɛ⁵¹,n</t>
   </si>
   <si>
     <t>zu5</t>
@@ -1267,7 +1267,7 @@
     <t>t͜sʰia³¹</t>
   </si>
   <si>
-    <t>i,a³¹</t>
+    <t>i,ˈa³¹</t>
   </si>
   <si>
     <t>nu2</t>
@@ -1300,7 +1300,7 @@
     <t>∅m̩⁵¹</t>
   </si>
   <si>
-    <t>m̩⁵¹</t>
+    <t>ˈm̩⁵¹</t>
   </si>
   <si>
     <t>m2</t>
@@ -1309,7 +1309,7 @@
     <t>∅m̩²⁴</t>
   </si>
   <si>
-    <t>m̩²⁴</t>
+    <t>ˈm̩²⁴</t>
   </si>
   <si>
     <t>m1</t>
@@ -1318,7 +1318,7 @@
     <t>∅m̩⁵⁴</t>
   </si>
   <si>
-    <t>m̩⁵⁴</t>
+    <t>ˈm̩⁵⁴</t>
   </si>
   <si>
     <t>vu5</t>
@@ -1345,7 +1345,7 @@
     <t>jɔn³¹</t>
   </si>
   <si>
-    <t>ɔ³¹,n</t>
+    <t>ˈɔ³¹,n</t>
   </si>
   <si>
     <t>ci3</t>
@@ -1360,7 +1360,7 @@
     <t>liɛt⁵</t>
   </si>
   <si>
-    <t>i,ɛ⁵,t</t>
+    <t>i,ˈɛ⁵,t</t>
   </si>
   <si>
     <t>shu2</t>
@@ -1381,7 +1381,7 @@
     <t>jau³¹</t>
   </si>
   <si>
-    <t>a³¹,u</t>
+    <t>ˈa³¹,u</t>
   </si>
   <si>
     <t>keu1</t>
@@ -1390,7 +1390,7 @@
     <t>kʰɛu⁵⁴</t>
   </si>
   <si>
-    <t>ɛ⁵⁴,u</t>
+    <t>ˈɛ⁵⁴,u</t>
   </si>
   <si>
     <t>ziu1</t>
@@ -1399,7 +1399,7 @@
     <t>t͜siu⁵⁴</t>
   </si>
   <si>
-    <t>i,u⁵⁴</t>
+    <t>i,ˈu⁵⁴</t>
   </si>
   <si>
     <t>leu2</t>
@@ -1408,7 +1408,7 @@
     <t>lɛu²⁴</t>
   </si>
   <si>
-    <t>ɛ²⁴,u</t>
+    <t>ˈɛ²⁴,u</t>
   </si>
   <si>
     <t>leu1</t>
@@ -1423,7 +1423,7 @@
     <t>lɛu³¹</t>
   </si>
   <si>
-    <t>ɛ³¹,u</t>
+    <t>ˈɛ³¹,u</t>
   </si>
   <si>
     <t>leu5</t>
@@ -1432,7 +1432,7 @@
     <t>lɛu⁵¹</t>
   </si>
   <si>
-    <t>ɛ⁵¹,u</t>
+    <t>ˈɛ⁵¹,u</t>
   </si>
   <si>
     <t>pu2</t>
@@ -1459,7 +1459,7 @@
     <t>t͜siu⁵¹</t>
   </si>
   <si>
-    <t>i,u⁵¹</t>
+    <t>i,ˈu⁵¹</t>
   </si>
   <si>
     <t>pu1</t>
@@ -1504,7 +1504,7 @@
     <t>mɔk³</t>
   </si>
   <si>
-    <t>ɔ³,k</t>
+    <t>ˈɔ³,k</t>
   </si>
   <si>
     <t>pok7</t>
@@ -1519,7 +1519,7 @@
     <t>pʰʊk³</t>
   </si>
   <si>
-    <t>ʊ³,k</t>
+    <t>ˈʊ³,k</t>
   </si>
   <si>
     <t>gu1</t>
@@ -1576,7 +1576,7 @@
     <t>lɛt³</t>
   </si>
   <si>
-    <t>ɛ³,t</t>
+    <t>ˈe³,t</t>
   </si>
   <si>
     <t>de1</t>
@@ -1615,7 +1615,7 @@
     <t>t͜sat³</t>
   </si>
   <si>
-    <t>a³,t</t>
+    <t>ˈa³,t</t>
   </si>
   <si>
     <t>shat8</t>
@@ -1624,7 +1624,7 @@
     <t>ʂat⁵</t>
   </si>
   <si>
-    <t>a⁵,t</t>
+    <t>ˈa⁵,t</t>
   </si>
   <si>
     <t>ge1</t>
@@ -1645,7 +1645,7 @@
     <t>hɛi⁵¹</t>
   </si>
   <si>
-    <t>ɛ⁵¹,i</t>
+    <t>ˈɛ⁵¹,i</t>
   </si>
   <si>
     <t>ei5</t>
@@ -1690,7 +1690,7 @@
     <t>hiak⁵</t>
   </si>
   <si>
-    <t>i,a⁵,k</t>
+    <t>i,ˈa⁵,k</t>
   </si>
   <si>
     <t>siak8</t>
@@ -1735,7 +1735,7 @@
     <t>kua⁵⁴</t>
   </si>
   <si>
-    <t>u,a⁵⁴</t>
+    <t>u,ˈa⁵⁴</t>
   </si>
   <si>
     <t>kua1</t>
@@ -1762,7 +1762,7 @@
     <t>ŋjai⁵¹</t>
   </si>
   <si>
-    <t>a⁵¹,i</t>
+    <t>ˈa⁵¹,i</t>
   </si>
   <si>
     <t>sai1</t>
@@ -1789,7 +1789,7 @@
     <t>kiɛt³</t>
   </si>
   <si>
-    <t>i,ɛ³,t</t>
+    <t>i,ˈe³,t</t>
   </si>
   <si>
     <t>kai3</t>
@@ -1840,7 +1840,7 @@
     <t>t͜sʰuai²⁴</t>
   </si>
   <si>
-    <t>u,a²⁴</t>
+    <t>u,ˈa²⁴</t>
   </si>
   <si>
     <t>zai1</t>
@@ -1891,7 +1891,7 @@
     <t>vun²⁴</t>
   </si>
   <si>
-    <t>u²⁴,n</t>
+    <t>ˈu²⁴,n</t>
   </si>
   <si>
     <t>kui3</t>
@@ -1930,7 +1930,7 @@
     <t>tun⁵⁴</t>
   </si>
   <si>
-    <t>u⁵⁴,n</t>
+    <t>ˈu⁵⁴,n</t>
   </si>
   <si>
     <t>poi2</t>
@@ -1975,7 +1975,7 @@
     <t>∅ɔi⁵¹</t>
   </si>
   <si>
-    <t>ɔ⁵¹,i</t>
+    <t>ˈɔ⁵¹,i</t>
   </si>
   <si>
     <t>goi1</t>
@@ -2026,7 +2026,7 @@
     <t>t͜sin⁵⁴</t>
   </si>
   <si>
-    <t>i⁵⁴,n</t>
+    <t>ˈi⁵⁴,n</t>
   </si>
   <si>
     <t>zin3</t>
@@ -2035,7 +2035,7 @@
     <t>t͜sin³¹</t>
   </si>
   <si>
-    <t>i³¹,n</t>
+    <t>ˈi³¹,n</t>
   </si>
   <si>
     <t>zin5</t>
@@ -2044,7 +2044,7 @@
     <t>t͜sin⁵¹</t>
   </si>
   <si>
-    <t>i⁵¹,n</t>
+    <t>ˈi⁵¹,n</t>
   </si>
   <si>
     <t>shun2</t>
@@ -2071,7 +2071,7 @@
     <t>jɛn⁵⁴</t>
   </si>
   <si>
-    <t>ɛ⁵⁴,n</t>
+    <t>ˈɛ⁵⁴,n</t>
   </si>
   <si>
     <t>jan1</t>
@@ -2080,7 +2080,7 @@
     <t>jan⁵⁴</t>
   </si>
   <si>
-    <t>a⁵⁴,n</t>
+    <t>ˈa⁵⁴,n</t>
   </si>
   <si>
     <t>sin1</t>
@@ -2155,7 +2155,7 @@
     <t>tʰiɛn²⁴</t>
   </si>
   <si>
-    <t>i,ɛ²⁴,n</t>
+    <t>i,ˈɛ²⁴,n</t>
   </si>
   <si>
     <t>cin5</t>
@@ -2236,7 +2236,7 @@
     <t>fun⁵¹</t>
   </si>
   <si>
-    <t>u⁵¹,n</t>
+    <t>ˈu⁵¹,n</t>
   </si>
   <si>
     <t>zun1</t>
@@ -2311,7 +2311,7 @@
     <t>liam²⁴</t>
   </si>
   <si>
-    <t>i,a²⁴,m</t>
+    <t>i,ˈa²⁴,m</t>
   </si>
   <si>
     <t>mun2</t>
@@ -2332,7 +2332,7 @@
     <t>jan²⁴</t>
   </si>
   <si>
-    <t>a²⁴,n</t>
+    <t>ˈa²⁴,n</t>
   </si>
   <si>
     <t>jen2</t>
@@ -2383,7 +2383,7 @@
     <t>pʰan⁵¹</t>
   </si>
   <si>
-    <t>a⁵¹,n</t>
+    <t>ˈa⁵¹,n</t>
   </si>
   <si>
     <t>hun1</t>
@@ -2416,7 +2416,7 @@
     <t>ŋjɔn⁵⁴</t>
   </si>
   <si>
-    <t>ɔ⁵⁴,n</t>
+    <t>ˈɔ⁵⁴,n</t>
   </si>
   <si>
     <t>jan5</t>
@@ -2455,7 +2455,7 @@
     <t>fan³¹</t>
   </si>
   <si>
-    <t>a³¹,n</t>
+    <t>ˈa³¹,n</t>
   </si>
   <si>
     <t>hien1</t>
@@ -2464,7 +2464,7 @@
     <t>hiɛn⁵⁴</t>
   </si>
   <si>
-    <t>i,ɛ⁵⁴,n</t>
+    <t>i,ˈɛ⁵⁴,n</t>
   </si>
   <si>
     <t>jan3</t>
@@ -2575,7 +2575,7 @@
     <t>hɔn²⁴</t>
   </si>
   <si>
-    <t>ɔ²⁴,n</t>
+    <t>ˈɔ²⁴,n</t>
   </si>
   <si>
     <t>hon5</t>
@@ -2584,7 +2584,7 @@
     <t>hɔn⁵¹</t>
   </si>
   <si>
-    <t>ɔ⁵¹,n</t>
+    <t>ˈɔ⁵¹,n</t>
   </si>
   <si>
     <t>ham2</t>
@@ -2593,7 +2593,7 @@
     <t>ham²⁴</t>
   </si>
   <si>
-    <t>a²⁴,m</t>
+    <t>ˈa²⁴,m</t>
   </si>
   <si>
     <t>ngon2</t>
@@ -2680,7 +2680,7 @@
     <t>tam³¹</t>
   </si>
   <si>
-    <t>a³¹,m</t>
+    <t>ˈa³¹,m</t>
   </si>
   <si>
     <t>gon5</t>
@@ -2773,7 +2773,7 @@
     <t>kuan⁵¹</t>
   </si>
   <si>
-    <t>u,a⁵¹,n</t>
+    <t>u,ˈa⁵¹,n</t>
   </si>
   <si>
     <t>guan1</t>
@@ -2782,7 +2782,7 @@
     <t>kuan⁵⁴</t>
   </si>
   <si>
-    <t>u,a⁵⁴,n</t>
+    <t>u,ˈa⁵⁴,n</t>
   </si>
   <si>
     <t>lon2</t>
@@ -2803,7 +2803,7 @@
     <t>kuɔn⁵¹</t>
   </si>
   <si>
-    <t>u,ɔ⁵¹,n</t>
+    <t>u,ˈɔ⁵¹,n</t>
   </si>
   <si>
     <t>zon1</t>
@@ -2872,7 +2872,7 @@
     <t>t͜sʰiaŋ³¹</t>
   </si>
   <si>
-    <t>i,a³¹,ŋ</t>
+    <t>i,ˈa³¹,ŋ</t>
   </si>
   <si>
     <t>zen3</t>
@@ -2881,7 +2881,7 @@
     <t>t͜sɛn³¹</t>
   </si>
   <si>
-    <t>ɛ³¹,n</t>
+    <t>ˈɛ³¹,n</t>
   </si>
   <si>
     <t>kuan2</t>
@@ -2890,7 +2890,7 @@
     <t>kʰuan²⁴</t>
   </si>
   <si>
-    <t>u,a²⁴,n</t>
+    <t>u,ˈa²⁴,n</t>
   </si>
   <si>
     <t>zan1</t>
@@ -2923,7 +2923,7 @@
     <t>t͜sʰiɛn³¹</t>
   </si>
   <si>
-    <t>i,ɛ³¹,n</t>
+    <t>i,ˈɛ³¹,n</t>
   </si>
   <si>
     <t>zien5</t>
@@ -2980,7 +2980,7 @@
     <t>siɛm⁵⁴</t>
   </si>
   <si>
-    <t>i,ɛ⁵⁴,m</t>
+    <t>i,ˈɛ⁵⁴,m</t>
   </si>
   <si>
     <t>hin2</t>
@@ -3013,7 +3013,7 @@
     <t>t͜sʰiɔn⁵¹</t>
   </si>
   <si>
-    <t>i,ɔ⁵¹,n</t>
+    <t>i,ˈɔ⁵¹,n</t>
   </si>
   <si>
     <t>lien5</t>
@@ -3058,7 +3058,7 @@
     <t>pʰiaŋ²⁴</t>
   </si>
   <si>
-    <t>i,a²⁴,ŋ</t>
+    <t>i,ˈa²⁴,ŋ</t>
   </si>
   <si>
     <t>zion1</t>
@@ -3067,7 +3067,7 @@
     <t>t͜siɔn⁵⁴</t>
   </si>
   <si>
-    <t>i,ɔ⁵⁴,n</t>
+    <t>i,ˈɔ⁵⁴,n</t>
   </si>
   <si>
     <t>njon2</t>
@@ -3100,7 +3100,7 @@
     <t>t͜sʰiɔn²⁴</t>
   </si>
   <si>
-    <t>i,ɔ²⁴,n</t>
+    <t>i,ˈɔ²⁴,n</t>
   </si>
   <si>
     <t>sion1</t>
@@ -3139,7 +3139,7 @@
     <t>siau⁵⁴</t>
   </si>
   <si>
-    <t>i,a⁵⁴</t>
+    <t>i,ˈa⁵⁴</t>
   </si>
   <si>
     <t>seu1</t>
@@ -3166,7 +3166,7 @@
     <t>tʰiau⁵¹</t>
   </si>
   <si>
-    <t>i,a⁵¹</t>
+    <t>i,ˈa⁵¹</t>
   </si>
   <si>
     <t>diau1</t>
@@ -3181,7 +3181,7 @@
     <t>tʰiau²⁴</t>
   </si>
   <si>
-    <t>i,a²⁴</t>
+    <t>i,ˈa²⁴</t>
   </si>
   <si>
     <t>hiau1</t>
@@ -3202,7 +3202,7 @@
     <t>t͜sau⁵⁴</t>
   </si>
   <si>
-    <t>a⁵⁴,u</t>
+    <t>ˈa⁵⁴,u</t>
   </si>
   <si>
     <t>jau1</t>
@@ -3277,7 +3277,7 @@
     <t>sau⁵¹</t>
   </si>
   <si>
-    <t>a⁵¹,u</t>
+    <t>ˈa⁵¹,u</t>
   </si>
   <si>
     <t>cau1</t>
@@ -3580,7 +3580,7 @@
     <t>t͜sʰiu²⁴</t>
   </si>
   <si>
-    <t>i,u²⁴</t>
+    <t>i,ˈu²⁴</t>
   </si>
   <si>
     <t>do1</t>
@@ -3715,7 +3715,7 @@
     <t>ŋap⁵</t>
   </si>
   <si>
-    <t>a⁵,p</t>
+    <t>ˈa⁵,p</t>
   </si>
   <si>
     <t>fa5</t>
@@ -3766,7 +3766,7 @@
     <t>lim²⁴</t>
   </si>
   <si>
-    <t>i²⁴,m</t>
+    <t>ˈi²⁴,m</t>
   </si>
   <si>
     <t>sha1</t>
@@ -3817,7 +3817,7 @@
     <t>vak⁵</t>
   </si>
   <si>
-    <t>a⁵,k</t>
+    <t>ˈa⁵,k</t>
   </si>
   <si>
     <t>ka1</t>
@@ -3838,7 +3838,7 @@
     <t>pa³¹</t>
   </si>
   <si>
-    <t>a³¹</t>
+    <t>ˈa³¹</t>
   </si>
   <si>
     <t>ba1</t>
@@ -3871,7 +3871,7 @@
     <t>jɔk⁵</t>
   </si>
   <si>
-    <t>ɔ⁵,k</t>
+    <t>ˈɔ⁵,k</t>
   </si>
   <si>
     <t>sia1</t>
@@ -3916,7 +3916,7 @@
     <t>jɔŋ³¹</t>
   </si>
   <si>
-    <t>ɔ³¹,ŋ</t>
+    <t>ˈɔ³¹,ŋ</t>
   </si>
   <si>
     <t>liong2</t>
@@ -3931,7 +3931,7 @@
     <t>liɔŋ⁵¹</t>
   </si>
   <si>
-    <t>i,ɔ⁵¹,ŋ</t>
+    <t>i,ˈɔ⁵¹,ŋ</t>
   </si>
   <si>
     <t>long2</t>
@@ -4030,7 +4030,7 @@
     <t>t͜siɔŋ³¹</t>
   </si>
   <si>
-    <t>i,ɔ³¹,ŋ</t>
+    <t>i,ˈɔ³¹,ŋ</t>
   </si>
   <si>
     <t>mong5</t>
@@ -4069,7 +4069,7 @@
     <t>kʰuɔŋ⁵⁴</t>
   </si>
   <si>
-    <t>u,ɔ⁵⁴,ŋ</t>
+    <t>u,ˈɔ⁵⁴,ŋ</t>
   </si>
   <si>
     <t>vong2</t>
@@ -4090,7 +4090,7 @@
     <t>kʰuɔŋ²⁴</t>
   </si>
   <si>
-    <t>u,ɔ²⁴,ŋ</t>
+    <t>u,ˈɔ²⁴,ŋ</t>
   </si>
   <si>
     <t>tong2</t>
@@ -4153,7 +4153,7 @@
     <t>vaŋ²⁴</t>
   </si>
   <si>
-    <t>a²⁴,ŋ</t>
+    <t>ˈa²⁴,ŋ</t>
   </si>
   <si>
     <t>fong3</t>
@@ -4198,7 +4198,7 @@
     <t>haŋ⁵⁴</t>
   </si>
   <si>
-    <t>a⁵⁴,ŋ</t>
+    <t>ˈa⁵⁴,ŋ</t>
   </si>
   <si>
     <t>ngong2</t>
@@ -4219,7 +4219,7 @@
     <t>kaŋ⁵¹</t>
   </si>
   <si>
-    <t>a⁵¹,ŋ</t>
+    <t>ˈa⁵¹,ŋ</t>
   </si>
   <si>
     <t>gang3</t>
@@ -4228,7 +4228,7 @@
     <t>kaŋ³¹</t>
   </si>
   <si>
-    <t>a³¹,ŋ</t>
+    <t>ˈa³¹,ŋ</t>
   </si>
   <si>
     <t>kang1</t>
@@ -4261,7 +4261,7 @@
     <t>kuaŋ⁵⁴</t>
   </si>
   <si>
-    <t>u,a⁵⁴,ŋ</t>
+    <t>u,ˈa⁵⁴,ŋ</t>
   </si>
   <si>
     <t>pang2</t>
@@ -4306,7 +4306,7 @@
     <t>kiaŋ⁵⁴</t>
   </si>
   <si>
-    <t>i,a⁵⁴,ŋ</t>
+    <t>i,ˈa⁵⁴,ŋ</t>
   </si>
   <si>
     <t>cang2</t>
@@ -4369,7 +4369,7 @@
     <t>t͜sʰiaŋ⁵¹</t>
   </si>
   <si>
-    <t>i,a⁵¹,ŋ</t>
+    <t>i,ˈa⁵¹,ŋ</t>
   </si>
   <si>
     <t>bung1</t>
@@ -4660,7 +4660,7 @@
     <t>t͜sʰiu³¹</t>
   </si>
   <si>
-    <t>i,u³¹</t>
+    <t>i,ˈu³¹</t>
   </si>
   <si>
     <t>shiu5</t>
@@ -4690,10 +4690,10 @@
     <t>but7</t>
   </si>
   <si>
-    <t>put³</t>
-  </si>
-  <si>
-    <t>u³,t</t>
+    <t>pʊt³</t>
+  </si>
+  <si>
+    <t>ˈʊ³,t</t>
   </si>
   <si>
     <t>hiu1</t>
@@ -4816,7 +4816,7 @@
     <t>jit⁵</t>
   </si>
   <si>
-    <t>i⁵,t</t>
+    <t>ˈɪ⁵,t</t>
   </si>
   <si>
     <t>geu3</t>
@@ -4855,7 +4855,7 @@
     <t>t͜sim⁵¹</t>
   </si>
   <si>
-    <t>i⁵¹,m</t>
+    <t>ˈi⁵¹,m</t>
   </si>
   <si>
     <t>siam1</t>
@@ -4864,7 +4864,7 @@
     <t>siam⁵⁴</t>
   </si>
   <si>
-    <t>i,a⁵⁴,m</t>
+    <t>i,ˈa⁵⁴,m</t>
   </si>
   <si>
     <t>cim2</t>
@@ -4885,7 +4885,7 @@
     <t>ʂim³¹</t>
   </si>
   <si>
-    <t>i³¹,m</t>
+    <t>ˈi³¹,m</t>
   </si>
   <si>
     <t>cam5</t>
@@ -4906,7 +4906,7 @@
     <t>t͜sɛm⁵⁴</t>
   </si>
   <si>
-    <t>ɛ⁵⁴,m</t>
+    <t>ˈɛ⁵⁴,m</t>
   </si>
   <si>
     <t>shim2</t>
@@ -4933,7 +4933,7 @@
     <t>nɛm³¹</t>
   </si>
   <si>
-    <t>ɛ³¹,m</t>
+    <t>ˈɛ³¹,m</t>
   </si>
   <si>
     <t>shim1</t>
@@ -5026,7 +5026,7 @@
     <t>t͜sʰam⁵⁴</t>
   </si>
   <si>
-    <t>a⁵⁴,m</t>
+    <t>ˈa⁵⁴,m</t>
   </si>
   <si>
     <t>cem2</t>
@@ -5035,7 +5035,7 @@
     <t>t͜sʰɛm²⁴</t>
   </si>
   <si>
-    <t>ɛ²⁴,m</t>
+    <t>ˈɛ²⁴,m</t>
   </si>
   <si>
     <t>cem1</t>
@@ -5140,7 +5140,7 @@
     <t>liam³¹</t>
   </si>
   <si>
-    <t>i,a³¹,m</t>
+    <t>i,ˈa³¹,m</t>
   </si>
   <si>
     <t>jam2</t>
@@ -5227,7 +5227,7 @@
     <t>t͜siam⁵¹</t>
   </si>
   <si>
-    <t>i,a⁵¹,m</t>
+    <t>i,ˈa⁵¹,m</t>
   </si>
   <si>
     <t>ciam2</t>
@@ -5272,7 +5272,7 @@
     <t>tiɛm⁵¹</t>
   </si>
   <si>
-    <t>i,ɛ⁵¹,m</t>
+    <t>i,ˈɛ⁵¹,m</t>
   </si>
   <si>
     <t>tiam2</t>
@@ -5569,7 +5569,7 @@
     <t>t͜sʰɔi³¹</t>
   </si>
   <si>
-    <t>ɔ³¹,i</t>
+    <t>ˈɔ³¹,i</t>
   </si>
   <si>
     <t>sui5</t>
@@ -5644,7 +5644,7 @@
     <t>∅ŋ̍³¹</t>
   </si>
   <si>
-    <t>ŋ̍³¹</t>
+    <t>ˈŋ̍³¹</t>
   </si>
   <si>
     <t>ju3</t>
@@ -5677,7 +5677,7 @@
     <t>sɔ³¹</t>
   </si>
   <si>
-    <t>ɔ³¹</t>
+    <t>ˈɔ³¹</t>
   </si>
   <si>
     <t>ja3</t>
@@ -5812,7 +5812,7 @@
     <t>tɛi³¹</t>
   </si>
   <si>
-    <t>ɛ³¹,i</t>
+    <t>ˈɛ³¹,i</t>
   </si>
   <si>
     <t>nai3</t>
@@ -5893,7 +5893,7 @@
     <t>kua³¹</t>
   </si>
   <si>
-    <t>u,a³¹</t>
+    <t>u,ˈa³¹</t>
   </si>
   <si>
     <t>fo3</t>
@@ -6082,7 +6082,7 @@
     <t>kʰun³¹</t>
   </si>
   <si>
-    <t>u³¹,n</t>
+    <t>ˈu³¹,n</t>
   </si>
   <si>
     <t>kun5</t>
@@ -6403,7 +6403,7 @@
     <t>kuan³¹</t>
   </si>
   <si>
-    <t>u,a³¹,n</t>
+    <t>u,ˈa³¹,n</t>
   </si>
   <si>
     <t>lon3</t>
@@ -6568,7 +6568,7 @@
     <t>t͜siɔn³¹</t>
   </si>
   <si>
-    <t>i,ɔ³¹,n</t>
+    <t>i,ˈɔ³¹,n</t>
   </si>
   <si>
     <t>lion3</t>
@@ -7087,7 +7087,7 @@
     <t>kuɔŋ³¹</t>
   </si>
   <si>
-    <t>u,ɔ³¹,ŋ</t>
+    <t>u,ˈɔ³¹,ŋ</t>
   </si>
   <si>
     <t>shong3</t>
@@ -7120,7 +7120,7 @@
     <t>kʰuɔŋ⁵¹</t>
   </si>
   <si>
-    <t>u,ɔ⁵¹,ŋ</t>
+    <t>u,ˈɔ⁵¹,ŋ</t>
   </si>
   <si>
     <t>nong3</t>
@@ -7201,7 +7201,7 @@
     <t>kuaŋ³¹</t>
   </si>
   <si>
-    <t>u,a³¹,ŋ</t>
+    <t>u,ˈa³¹,ŋ</t>
   </si>
   <si>
     <t>bang3</t>
@@ -7594,7 +7594,7 @@
     <t>t͜sʰɛm⁵¹</t>
   </si>
   <si>
-    <t>ɛ⁵¹,m</t>
+    <t>ˈɛ⁵¹,m</t>
   </si>
   <si>
     <t>gam3</t>
@@ -7735,7 +7735,7 @@
     <t>liɛm³¹</t>
   </si>
   <si>
-    <t>i,ɛ³¹,m</t>
+    <t>i,ˈɛ³¹,m</t>
   </si>
   <si>
     <t>hiam5</t>
@@ -7798,7 +7798,7 @@
     <t>t͜sit³</t>
   </si>
   <si>
-    <t>i³,t</t>
+    <t>ˈɪ³,t</t>
   </si>
   <si>
     <t>nji5</t>
@@ -7861,13 +7861,13 @@
     <t>fʊk⁵</t>
   </si>
   <si>
-    <t>ʊ⁵,k</t>
+    <t>ˈʊ⁵,k</t>
   </si>
   <si>
     <t>sut7</t>
   </si>
   <si>
-    <t>sut³</t>
+    <t>sʊt³</t>
   </si>
   <si>
     <t>ni5</t>
@@ -7888,7 +7888,7 @@
     <t>∅n̩⁵¹</t>
   </si>
   <si>
-    <t>n̩⁵¹</t>
+    <t>ˈn̩⁵¹</t>
   </si>
   <si>
     <t>cit8</t>
@@ -7906,7 +7906,7 @@
     <t>cut7</t>
   </si>
   <si>
-    <t>t͜sʰut³</t>
+    <t>t͜sʰʊt³</t>
   </si>
   <si>
     <t>shit7</t>
@@ -7927,7 +7927,7 @@
     <t>ʂik⁵</t>
   </si>
   <si>
-    <t>i⁵,k</t>
+    <t>ˈɪ⁵,k</t>
   </si>
   <si>
     <t>gi2</t>
@@ -7972,7 +7972,7 @@
     <t>∅ŋ̍⁵¹</t>
   </si>
   <si>
-    <t>ŋ̍⁵¹</t>
+    <t>ˈŋ̍⁵¹</t>
   </si>
   <si>
     <t>ngu5</t>
@@ -8077,7 +8077,7 @@
     <t>ʂɔt³</t>
   </si>
   <si>
-    <t>ɔ³,t</t>
+    <t>ˈɔ³,t</t>
   </si>
   <si>
     <t>piet8</t>
@@ -8158,7 +8158,7 @@
     <t>kʰuai⁵¹</t>
   </si>
   <si>
-    <t>u,a⁵¹</t>
+    <t>u,ˈa⁵¹</t>
   </si>
   <si>
     <t>ngoi5</t>
@@ -8653,7 +8653,7 @@
     <t>liɔt³</t>
   </si>
   <si>
-    <t>i,ɔ³,t</t>
+    <t>i,ˈɔ³,t</t>
   </si>
   <si>
     <t>njong5</t>
@@ -8968,7 +8968,7 @@
     <t>tʰiap³</t>
   </si>
   <si>
-    <t>i,a³,p</t>
+    <t>i,ˈa³,p</t>
   </si>
   <si>
     <t>siam5</t>
@@ -9175,7 +9175,7 @@
     <t>kʰiɔk³</t>
   </si>
   <si>
-    <t>i,ɔ³,k</t>
+    <t>i,ˈɔ³,k</t>
   </si>
   <si>
     <t>sok7</t>
@@ -9271,10 +9271,10 @@
     <t>kiut7</t>
   </si>
   <si>
-    <t>kʰiut³</t>
-  </si>
-  <si>
-    <t>i,u³,t</t>
+    <t>kʰiʊt³</t>
+  </si>
+  <si>
+    <t>i,ˈʊ³,t</t>
   </si>
   <si>
     <t>hit7</t>
@@ -9295,7 +9295,7 @@
     <t>mɛt⁵</t>
   </si>
   <si>
-    <t>ɛ⁵,t</t>
+    <t>ˈɛ⁵,t</t>
   </si>
   <si>
     <t>mit8</t>
@@ -9325,16 +9325,16 @@
     <t>jut8</t>
   </si>
   <si>
-    <t>jut⁵</t>
-  </si>
-  <si>
-    <t>u⁵,t</t>
+    <t>jʊt⁵</t>
+  </si>
+  <si>
+    <t>ˈʊ⁵,t</t>
   </si>
   <si>
     <t>siut7</t>
   </si>
   <si>
-    <t>siut³</t>
+    <t>siʊt³</t>
   </si>
   <si>
     <t>jat7</t>
@@ -9346,88 +9346,88 @@
     <t>njut8</t>
   </si>
   <si>
-    <t>ŋjut⁵</t>
+    <t>ŋjʊt⁵</t>
   </si>
   <si>
     <t>zut7</t>
   </si>
   <si>
-    <t>t͜sut³</t>
+    <t>t͜sʊt³</t>
   </si>
   <si>
     <t>fut7</t>
   </si>
   <si>
-    <t>fut³</t>
+    <t>fʊt³</t>
   </si>
   <si>
     <t>shut8</t>
   </si>
   <si>
-    <t>ʂut⁵</t>
+    <t>ʂʊt⁵</t>
   </si>
   <si>
     <t>sut8</t>
   </si>
   <si>
-    <t>sut⁵</t>
+    <t>sʊt⁵</t>
   </si>
   <si>
     <t>cut8</t>
   </si>
   <si>
-    <t>t͜sʰut⁵</t>
+    <t>t͜sʰʊt⁵</t>
   </si>
   <si>
     <t>lut8</t>
   </si>
   <si>
-    <t>lut⁵</t>
+    <t>lʊt⁵</t>
   </si>
   <si>
     <t>liut8</t>
   </si>
   <si>
-    <t>liut⁵</t>
-  </si>
-  <si>
-    <t>i,u⁵,t</t>
+    <t>liʊt⁵</t>
+  </si>
+  <si>
+    <t>i,ˈʊ⁵,t</t>
   </si>
   <si>
     <t>ziut7</t>
   </si>
   <si>
-    <t>t͜siut³</t>
+    <t>t͜siʊt³</t>
   </si>
   <si>
     <t>vut8</t>
   </si>
   <si>
-    <t>vut⁵</t>
+    <t>vʊt⁵</t>
   </si>
   <si>
     <t>mut8</t>
   </si>
   <si>
-    <t>mut⁵</t>
+    <t>mʊt⁵</t>
   </si>
   <si>
     <t>jut7</t>
   </si>
   <si>
-    <t>jut³</t>
+    <t>jʊt³</t>
   </si>
   <si>
     <t>vut7</t>
   </si>
   <si>
-    <t>vut³</t>
+    <t>vʊt³</t>
   </si>
   <si>
     <t>gut7</t>
   </si>
   <si>
-    <t>kut³</t>
+    <t>kʊt³</t>
   </si>
   <si>
     <t>kiet8</t>
@@ -9439,13 +9439,13 @@
     <t>kiut8</t>
   </si>
   <si>
-    <t>kʰiut⁵</t>
+    <t>kʰiʊt⁵</t>
   </si>
   <si>
     <t>fut8</t>
   </si>
   <si>
-    <t>fut⁵</t>
+    <t>fʊt⁵</t>
   </si>
   <si>
     <t>gat8</t>
@@ -9472,7 +9472,7 @@
     <t>jɔt⁵</t>
   </si>
   <si>
-    <t>ɔ⁵,t</t>
+    <t>ˈɔ⁵,t</t>
   </si>
   <si>
     <t>fat8</t>
@@ -9550,7 +9550,7 @@
     <t>tut7</t>
   </si>
   <si>
-    <t>tʰut³</t>
+    <t>tʰʊt³</t>
   </si>
   <si>
     <t>vat8</t>
@@ -9562,43 +9562,43 @@
     <t>put8</t>
   </si>
   <si>
-    <t>pʰut⁵</t>
+    <t>pʰʊt⁵</t>
   </si>
   <si>
     <t>dut7</t>
   </si>
   <si>
-    <t>tut³</t>
+    <t>tʊt³</t>
   </si>
   <si>
     <t>tut8</t>
   </si>
   <si>
-    <t>tʰut⁵</t>
+    <t>tʰʊt⁵</t>
   </si>
   <si>
     <t>ngut8</t>
   </si>
   <si>
-    <t>ŋut⁵</t>
+    <t>ŋʊt⁵</t>
   </si>
   <si>
     <t>put7</t>
   </si>
   <si>
-    <t>pʰut³</t>
+    <t>pʰʊt³</t>
   </si>
   <si>
     <t>kut7</t>
   </si>
   <si>
-    <t>kʰut³</t>
+    <t>kʰʊt³</t>
   </si>
   <si>
     <t>nut8</t>
   </si>
   <si>
-    <t>nut⁵</t>
+    <t>nʊt⁵</t>
   </si>
   <si>
     <t>het8</t>
@@ -9691,7 +9691,7 @@
     <t>kuat³</t>
   </si>
   <si>
-    <t>u,a³,t</t>
+    <t>u,ˈa³,t</t>
   </si>
   <si>
     <t>kuat7</t>
@@ -9778,7 +9778,7 @@
     <t>ŋuat⁵</t>
   </si>
   <si>
-    <t>u,a⁵,t</t>
+    <t>u,ˈa⁵,t</t>
   </si>
   <si>
     <t>tit8</t>
@@ -9799,7 +9799,7 @@
     <t>ʂiat³</t>
   </si>
   <si>
-    <t>i,a³,t</t>
+    <t>i,ˈa³,t</t>
   </si>
   <si>
     <t>tiat8</t>
@@ -9808,7 +9808,7 @@
     <t>tʰiat⁵</t>
   </si>
   <si>
-    <t>i,a⁵,t</t>
+    <t>i,ˈa⁵,t</t>
   </si>
   <si>
     <t>diet7</t>
@@ -9901,7 +9901,7 @@
     <t>liɔt⁵</t>
   </si>
   <si>
-    <t>i,ɔ⁵,t</t>
+    <t>i,ˈɔ⁵,t</t>
   </si>
   <si>
     <t>shat7</t>
@@ -9934,7 +9934,7 @@
     <t>liɔk⁵</t>
   </si>
   <si>
-    <t>i,ɔ⁵,k</t>
+    <t>i,ˈɔ⁵,k</t>
   </si>
   <si>
     <t>liok7</t>
@@ -9985,7 +9985,7 @@
     <t>t͜sʰiak³</t>
   </si>
   <si>
-    <t>i,a³,k</t>
+    <t>i,ˈa³,k</t>
   </si>
   <si>
     <t>ciok7</t>
@@ -10018,7 +10018,7 @@
     <t>kuɔk³</t>
   </si>
   <si>
-    <t>u,ɔ³,k</t>
+    <t>u,ˈɔ³,k</t>
   </si>
   <si>
     <t>kuok7</t>
@@ -10033,7 +10033,7 @@
     <t>kʰuɔk⁵</t>
   </si>
   <si>
-    <t>u,ɔ⁵,k</t>
+    <t>u,ˈɔ⁵,k</t>
   </si>
   <si>
     <t>niok8</t>
@@ -10102,7 +10102,7 @@
     <t>fɛk⁵</t>
   </si>
   <si>
-    <t>ɛ⁵,k</t>
+    <t>ˈɛ⁵,k</t>
   </si>
   <si>
     <t>nguok8</t>
@@ -10141,7 +10141,7 @@
     <t>kɛk³</t>
   </si>
   <si>
-    <t>ɛ³,k</t>
+    <t>ˈe³,k</t>
   </si>
   <si>
     <t>kik8</t>
@@ -10252,7 +10252,7 @@
     <t>fɛk⁵⁴</t>
   </si>
   <si>
-    <t>ɛ⁵⁴,k</t>
+    <t>ˈɛ⁵⁴,k</t>
   </si>
   <si>
     <t>fak8</t>
@@ -10375,7 +10375,7 @@
     <t>hiɛk⁵</t>
   </si>
   <si>
-    <t>i,ɛ⁵,k</t>
+    <t>i,ˈɛ⁵,k</t>
   </si>
   <si>
     <t>njik8</t>
@@ -10408,7 +10408,7 @@
     <t>t͜sʰiɛk³</t>
   </si>
   <si>
-    <t>i,ɛ³,k</t>
+    <t>i,ˈe³,k</t>
   </si>
   <si>
     <t>tek7</t>
@@ -10555,7 +10555,7 @@
     <t>t͜sʰip³</t>
   </si>
   <si>
-    <t>i³,p</t>
+    <t>ˈɪ³,p</t>
   </si>
   <si>
     <t>ship8</t>
@@ -10564,7 +10564,7 @@
     <t>ʂip⁵</t>
   </si>
   <si>
-    <t>i⁵,p</t>
+    <t>ˈɪ⁵,p</t>
   </si>
   <si>
     <t>zip7</t>
@@ -10645,7 +10645,7 @@
     <t>sɛp³</t>
   </si>
   <si>
-    <t>ɛ³,p</t>
+    <t>ˈe³,p</t>
   </si>
   <si>
     <t>hip7</t>
@@ -10768,7 +10768,7 @@
     <t>ʂiɛp⁵</t>
   </si>
   <si>
-    <t>i,ɛ⁵,p</t>
+    <t>i,ˈɛ⁵,p</t>
   </si>
   <si>
     <t>ziap7</t>
@@ -10891,7 +10891,7 @@
     <t>siɛp³</t>
   </si>
   <si>
-    <t>i,ɛ³,p</t>
+    <t>i,ˈe³,p</t>
   </si>
   <si>
     <t>liep8</t>
@@ -11038,7 +11038,7 @@
     <t>∅n̩²⁴</t>
   </si>
   <si>
-    <t>n̩²⁴</t>
+    <t>ˈn̩¹³</t>
   </si>
   <si>
     <t>gan5</t>
@@ -11065,7 +11065,7 @@
     <t>hm̩³¹</t>
   </si>
   <si>
-    <t>m̩³¹</t>
+    <t>ˈm̩³¹</t>
   </si>
   <si>
     <t>ni1</t>
@@ -11134,7 +11134,7 @@
     <t>jat⁵⁴</t>
   </si>
   <si>
-    <t>a⁵⁴,t</t>
+    <t>ˈa⁵⁴,t</t>
   </si>
   <si>
     <t>ting2</t>
@@ -11143,7 +11143,7 @@
     <t>tʰiŋ²⁴</t>
   </si>
   <si>
-    <t>i²⁴,ŋ</t>
+    <t>ˈi²⁴,ŋ</t>
   </si>
   <si>
     <t>ngen5</t>
@@ -11158,7 +11158,7 @@
     <t>tə⁵¹</t>
   </si>
   <si>
-    <t>ə⁵¹</t>
+    <t>ˈə⁵¹</t>
   </si>
   <si>
     <t>ler5</t>
@@ -11173,7 +11173,7 @@
     <t>lə⁵⁴</t>
   </si>
   <si>
-    <t>ə⁵⁴</t>
+    <t>ˈə⁵⁴</t>
   </si>
   <si>
     <t>bai2</t>
@@ -11215,16 +11215,16 @@
     <t>kut8</t>
   </si>
   <si>
-    <t>kʰut⁵</t>
+    <t>kʰʊt⁵</t>
   </si>
   <si>
     <t>but1</t>
   </si>
   <si>
-    <t>put⁵⁴</t>
-  </si>
-  <si>
-    <t>u⁵⁴,t</t>
+    <t>pʊt⁵⁴</t>
+  </si>
+  <si>
+    <t>ˈʊ⁵⁴,t</t>
   </si>
   <si>
     <t>lang3</t>
@@ -11237,6 +11237,174 @@
   </si>
   <si>
     <t>ŋjʊŋ⁵⁴</t>
+  </si>
+  <si>
+    <t>bet7</t>
+  </si>
+  <si>
+    <t>pɛt³</t>
+  </si>
+  <si>
+    <t>biak7</t>
+  </si>
+  <si>
+    <t>piak³</t>
+  </si>
+  <si>
+    <t>cet8</t>
+  </si>
+  <si>
+    <t>t͜sʰɛt⁵</t>
+  </si>
+  <si>
+    <t>ciat7</t>
+  </si>
+  <si>
+    <t>t͜sʰiat³</t>
+  </si>
+  <si>
+    <t>det7</t>
+  </si>
+  <si>
+    <t>tɛt³</t>
+  </si>
+  <si>
+    <t>fet8</t>
+  </si>
+  <si>
+    <t>fɛt⁵</t>
+  </si>
+  <si>
+    <t>gai2</t>
+  </si>
+  <si>
+    <t>kai²⁴</t>
+  </si>
+  <si>
+    <t>get7</t>
+  </si>
+  <si>
+    <t>kɛt³</t>
+  </si>
+  <si>
+    <t>gia1</t>
+  </si>
+  <si>
+    <t>kia⁵⁴</t>
+  </si>
+  <si>
+    <t>guk8</t>
+  </si>
+  <si>
+    <t>kʊk⁵</t>
+  </si>
+  <si>
+    <t>hai1</t>
+  </si>
+  <si>
+    <t>hai⁵⁴</t>
+  </si>
+  <si>
+    <t>het7</t>
+  </si>
+  <si>
+    <t>hɛt³</t>
+  </si>
+  <si>
+    <t>iun5</t>
+  </si>
+  <si>
+    <t>∅iun⁵¹</t>
+  </si>
+  <si>
+    <t>i,ˈu⁵¹,n</t>
+  </si>
+  <si>
+    <t>koi1</t>
+  </si>
+  <si>
+    <t>kʰɔi⁵⁴</t>
+  </si>
+  <si>
+    <t>let8</t>
+  </si>
+  <si>
+    <t>lɛt⁵</t>
+  </si>
+  <si>
+    <t>me5</t>
+  </si>
+  <si>
+    <t>mɛi⁵¹</t>
+  </si>
+  <si>
+    <t>mei1</t>
+  </si>
+  <si>
+    <t>ngi1</t>
+  </si>
+  <si>
+    <t>ngi2</t>
+  </si>
+  <si>
+    <t>ngi5</t>
+  </si>
+  <si>
+    <t>niong2</t>
+  </si>
+  <si>
+    <t>niɔŋ²⁴</t>
+  </si>
+  <si>
+    <t>shot8</t>
+  </si>
+  <si>
+    <t>ʂɔt⁵</t>
+  </si>
+  <si>
+    <t>shung2</t>
+  </si>
+  <si>
+    <t>ʂʊŋ²⁴</t>
+  </si>
+  <si>
+    <t>tau1</t>
+  </si>
+  <si>
+    <t>tʰau⁵⁴</t>
+  </si>
+  <si>
+    <t>tet7</t>
+  </si>
+  <si>
+    <t>tʰɛt³</t>
+  </si>
+  <si>
+    <t>tet8</t>
+  </si>
+  <si>
+    <t>tʰɛt⁵</t>
+  </si>
+  <si>
+    <t>ung1</t>
+  </si>
+  <si>
+    <t>∅ʊŋ⁵⁴</t>
+  </si>
+  <si>
+    <t>zat8</t>
+  </si>
+  <si>
+    <t>t͜sat⁵</t>
+  </si>
+  <si>
+    <t>zik3</t>
+  </si>
+  <si>
+    <t>t͜sik³¹</t>
+  </si>
+  <si>
+    <t>ˈi³¹,k</t>
   </si>
 </sst>
 </file>
@@ -11568,7 +11736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1763"/>
+  <dimension ref="A1:D1792"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36253,6 +36421,412 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1764" spans="1:4">
+      <c r="A1764" t="s">
+        <v>3741</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>3742</v>
+      </c>
+      <c r="C1764" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1764" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:4">
+      <c r="A1765" t="s">
+        <v>3743</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>3744</v>
+      </c>
+      <c r="C1765" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1765" t="s">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:4">
+      <c r="A1766" t="s">
+        <v>3745</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>3746</v>
+      </c>
+      <c r="C1766" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1766" t="s">
+        <v>3093</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:4">
+      <c r="A1767" t="s">
+        <v>3747</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>3748</v>
+      </c>
+      <c r="C1767" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1767" t="s">
+        <v>3261</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:4">
+      <c r="A1768" t="s">
+        <v>3749</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>3750</v>
+      </c>
+      <c r="C1768" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1768" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:4">
+      <c r="A1769" t="s">
+        <v>3751</v>
+      </c>
+      <c r="B1769" t="s">
+        <v>3752</v>
+      </c>
+      <c r="C1769" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1769" t="s">
+        <v>3093</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:4">
+      <c r="A1770" t="s">
+        <v>3753</v>
+      </c>
+      <c r="B1770" t="s">
+        <v>3754</v>
+      </c>
+      <c r="C1770" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1770" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:4">
+      <c r="A1771" t="s">
+        <v>3755</v>
+      </c>
+      <c r="B1771" t="s">
+        <v>3756</v>
+      </c>
+      <c r="C1771" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1771" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:4">
+      <c r="A1772" t="s">
+        <v>3757</v>
+      </c>
+      <c r="B1772" t="s">
+        <v>3758</v>
+      </c>
+      <c r="C1772" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1772" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:4">
+      <c r="A1773" t="s">
+        <v>3759</v>
+      </c>
+      <c r="B1773" t="s">
+        <v>3760</v>
+      </c>
+      <c r="C1773" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1773" t="s">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:4">
+      <c r="A1774" t="s">
+        <v>3761</v>
+      </c>
+      <c r="B1774" t="s">
+        <v>3762</v>
+      </c>
+      <c r="C1774" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1774" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:4">
+      <c r="A1775" t="s">
+        <v>3763</v>
+      </c>
+      <c r="B1775" t="s">
+        <v>3764</v>
+      </c>
+      <c r="C1775" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1775" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:4">
+      <c r="A1776" t="s">
+        <v>3765</v>
+      </c>
+      <c r="B1776" t="s">
+        <v>3766</v>
+      </c>
+      <c r="C1776" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1776" t="s">
+        <v>3767</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:4">
+      <c r="A1777" t="s">
+        <v>3768</v>
+      </c>
+      <c r="B1777" t="s">
+        <v>3769</v>
+      </c>
+      <c r="C1777" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1777" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:4">
+      <c r="A1778" t="s">
+        <v>3770</v>
+      </c>
+      <c r="B1778" t="s">
+        <v>3771</v>
+      </c>
+      <c r="C1778" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1778" t="s">
+        <v>3093</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:4">
+      <c r="A1779" t="s">
+        <v>3772</v>
+      </c>
+      <c r="B1779" t="s">
+        <v>3773</v>
+      </c>
+      <c r="C1779" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1779" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:4">
+      <c r="A1780" t="s">
+        <v>3774</v>
+      </c>
+      <c r="B1780" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C1780" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1780" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:4">
+      <c r="A1781" t="s">
+        <v>3775</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>547</v>
+      </c>
+      <c r="C1781" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1781" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:4">
+      <c r="A1782" t="s">
+        <v>3776</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1782" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1782" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:4">
+      <c r="A1783" t="s">
+        <v>3777</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>2596</v>
+      </c>
+      <c r="C1783" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1783" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:4">
+      <c r="A1784" t="s">
+        <v>3778</v>
+      </c>
+      <c r="B1784" t="s">
+        <v>3779</v>
+      </c>
+      <c r="C1784" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1784" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:4">
+      <c r="A1785" t="s">
+        <v>3780</v>
+      </c>
+      <c r="B1785" t="s">
+        <v>3781</v>
+      </c>
+      <c r="C1785" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1785" t="s">
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:4">
+      <c r="A1786" t="s">
+        <v>3782</v>
+      </c>
+      <c r="B1786" t="s">
+        <v>3783</v>
+      </c>
+      <c r="C1786" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1786" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:4">
+      <c r="A1787" t="s">
+        <v>3784</v>
+      </c>
+      <c r="B1787" t="s">
+        <v>3785</v>
+      </c>
+      <c r="C1787" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1787" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:4">
+      <c r="A1788" t="s">
+        <v>3786</v>
+      </c>
+      <c r="B1788" t="s">
+        <v>3787</v>
+      </c>
+      <c r="C1788" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1788" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:4">
+      <c r="A1789" t="s">
+        <v>3788</v>
+      </c>
+      <c r="B1789" t="s">
+        <v>3789</v>
+      </c>
+      <c r="C1789" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1789" t="s">
+        <v>3093</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:4">
+      <c r="A1790" t="s">
+        <v>3790</v>
+      </c>
+      <c r="B1790" t="s">
+        <v>3791</v>
+      </c>
+      <c r="C1790" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1790" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:4">
+      <c r="A1791" t="s">
+        <v>3792</v>
+      </c>
+      <c r="B1791" t="s">
+        <v>3793</v>
+      </c>
+      <c r="C1791" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1791" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:4">
+      <c r="A1792" t="s">
+        <v>3794</v>
+      </c>
+      <c r="B1792" t="s">
+        <v>3795</v>
+      </c>
+      <c r="C1792" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1792" t="s">
+        <v>3796</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
